--- a/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/9.责任矩阵信息.xlsx
+++ b/data/projects/56A0TXN/早期介入/交付预案/解析结果/预案草稿/9.责任矩阵信息.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,7 +471,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>计划管理</t>
+          <t>计划进度管理、沟通管理、风险管理、变更管理、问题管理、质量管理、采购管理、验收管理等</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -479,11 +479,7 @@
           <t>R</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>S</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
           <t>S</t>
@@ -491,10 +487,1792 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>S</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>计算-工程安装</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>工程勘测</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>计算-工程安装</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>设备签收</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>计算-工程安装</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>硬件部署</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>计算-工程安装</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>硬件初始化</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>计算-工程安装</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>固件升级</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>计算-工程安装</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>硬件压测</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>计算-工程安装</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>硬件验收</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>规划设计</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>OS安装</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>计算服务软件安装</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>单机综合测试</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>单机测试</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>管理子系统验收</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>项目管理</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>站点工勘</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>需求调研</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>硬件安装</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>计算-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>系统部署</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>硬件底座</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>存储-规划设计与集成</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>存储网络连接</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>硬件底座</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>存储-规划设计与集成</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>基础功能配置</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>硬件底座</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>存储-规划设计与集成</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>增值特性配置</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>硬件底座</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>存储-规划设计与集成</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>验收方案</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>硬件底座</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>存储-规划设计与集成</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>验收测试</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>硬件底座</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>存储-规划设计与集成</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>项目移交</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>硬件底座</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>存储-规划设计与集成</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>存储升级</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>硬件底座</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>网络-工程安装</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>工程安装</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>硬件底座</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>网络-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>规划设计与实施</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>集群系统需求调研</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>集群系统规划设计</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>集群系统对接联网</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>参数面集合通信测试</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>集群性能测试</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>集群稳定性测试（训练）</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>集群初始化调优（训练）</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>集群试运行（可选）</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>集群验收</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>需求环境调研</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>算存网</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>算存网-集群集成</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>云网规划设计</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HCS+ModelArts-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>云服务设计</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HCS+ModelArts-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>资源池设计</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HCS+ModelArts-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>LLD设计</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HCS+ModelArts-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>HCS安装实施</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HCS+ModelArts-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ModelArts安装实施</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HCS+ModelArts-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>平台测试与验收支持</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>DCS-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>需求分析</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>DCS-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>整体规划</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>DCS-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>系统设计</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>DCS-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>集成实施</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>DCS-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>项目验收</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>AI平台</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>DCS-规划设计与实施</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>系统移交</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>AI计算使能-模型部署支持</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>模型部署支持-训练</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>AI计算使能-模型部署支持</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>模型部署支持-推理</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>AI计算使能-AI计算软件栈技术支持</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>问题定位</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>AI计算使能-AI计算软件栈技术支持</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>使用支持</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>AI计算使能-模型部署样例演示</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>人员组织，协调场地环境</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>AI计算使能-模型部署样例演示</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>开发环境搭建演示</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>模型</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>AI计算使能-模型部署样例演示</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>模型部署演示</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>应用</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr"/>
+      <c r="H61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>初验PAC</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>签发初验PAC</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr"/>
+      <c r="H62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>公共</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>终验FAC</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>签发终验FAC</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>R/A</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
